--- a/data/processed/harmonization/Acidity__Soil_pH/10.15485_1785525/10.15485_1785525_soil_Acidity__Soil_pH.xlsx
+++ b/data/processed/harmonization/Acidity__Soil_pH/10.15485_1785525/10.15485_1785525_soil_Acidity__Soil_pH.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="54" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -3158,12 +3158,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3:3</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -3302,12 +3302,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4:4</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -3350,12 +3350,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5:5</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -3398,12 +3398,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1:6</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2:7</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3:8</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
@@ -3542,12 +3542,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4:9</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5:10</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6:11</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8:12</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -3782,12 +3782,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -3830,12 +3830,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
